--- a/extenbooks/ES2001_extenbook.xlsx
+++ b/extenbooks/ES2001_extenbook.xlsx
@@ -4145,7 +4145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A156"/>
+  <dimension ref="A1:A185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4205,7 +4205,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>## 6. Source-URL substitutions</t>
+          <t>## 6. Conceptual continuity vs adjacent concepts</t>
         </is>
       </c>
     </row>
@@ -5026,43 +5026,234 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Per decision 0005 / CHES adequacy: `anwarshaikhecon.org` was DNS-</t>
+          <t>The extension proxy (v1.1 shared BEA-to-Sraffa pipeline) measures</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>unreachable 2026-05-18. The canonical URL-of-record for ES2001 is</t>
+          <t>`Sraffa aggregate price/value ratios at observed rates of profit` rather</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>the archival PDF at:</t>
+          <t>than `nominal-vs-real GDP ratios` or `Marx-Tonak constant/variable</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>`Inputs/Capitalism Data/Technical/data/raw/01_SOURCE_MATERIALS/Web Folders/Shaikh Publications/[2020] Shaikh - An Empirically Sufficient Form for Sraffa Prices.pdf`</t>
+          <t>capital aggregates` because:</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>- Source agency choice: BEA Benchmark IO Use/Make tables are the input</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Festschrift volume metadata per paper's own reference list (p. 20):</t>
+          <t xml:space="preserve">  to the paper's eqs 6, 8, 10. No alternative agency exists for the</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  industry-level technology matrix needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>- Methodology continuity: the v1.0 verbatim Tables 1-2 panel and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  v1.1 extended panel both run *the same* eigenvalue/left-eigenvector</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  computation on *the same* BEA-IO matrix family. Adding 1977/1982/.../2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  benchmark years is concept-identical, not concept-substituting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>- Disambiguation: aggregate price/value ratios are NOT cross-sectional</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Sraffa price curves p(r) — those are ES2101's empirical object.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tables 1-2 collapse the curve to a single scalar at r_obs per</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (model, year). Extension preserves the scalar concept; the curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  concept lives in a sibling series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>The book's original concept (Shaikh 2020 p. 9, "The Six Benchmark Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Tables") was: "the close empirical correspondence between Sraffa prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>and labor values across the entire empirically observed range of the rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>of profit". The modern series preserves the scalar aggregate-ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>computation while permitting matrix-order discontinuities (71-order</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>for 1947-1972, 65-order for 1998, 403/171-order for 2002+). This is NOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>a proxy substitution forbidden by the No-Proxy rule because BEA IO is</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>the canonical and only source of the input; extension years use exactly</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>the same source family at successive vintages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>## 7. Source-URL substitutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Per decision 0005 / CHES adequacy: `anwarshaikhecon.org` was DNS-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>unreachable 2026-05-18. The canonical URL-of-record for ES2001 is</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>the archival PDF at:</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>`Inputs/Capitalism Data/Technical/data/raw/01_SOURCE_MATERIALS/Web Folders/Shaikh Publications/[2020] Shaikh - An Empirically Sufficient Form for Sraffa Prices.pdf`</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Festschrift volume metadata per paper's own reference list (p. 20):</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
         <is>
           <t>Velupillai (ed.), Palgrave Macmillan. DOI pinning is a v1.1 task.</t>
         </is>
@@ -5146,14 +5337,42 @@
           <t>ES2001-circ-constant_capital</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5161,14 +5380,42 @@
           <t>ES2001-circ-max_rate_profit_R</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5176,14 +5423,42 @@
           <t>ES2001-circ-r_obs</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5191,14 +5466,42 @@
           <t>ES2001-circ-r_obs_over_R</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5249,14 +5552,42 @@
           <t>ES2001-circ-rate_surplus_value</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5264,14 +5595,42 @@
           <t>ES2001-circ-surplus_value</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5279,14 +5638,42 @@
           <t>ES2001-circ-value_added</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5294,14 +5681,42 @@
           <t>ES2001-circ-variable_capital</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5309,14 +5724,42 @@
           <t>ES2001-fixed-constant_capital</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5324,14 +5767,42 @@
           <t>ES2001-fixed-max_rate_profit_R</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5339,14 +5810,42 @@
           <t>ES2001-fixed-r_obs</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5354,14 +5853,42 @@
           <t>ES2001-fixed-r_obs_over_R</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5412,14 +5939,42 @@
           <t>ES2001-fixed-rate_surplus_value</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5427,14 +5982,42 @@
           <t>ES2001-fixed-surplus_value</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5442,14 +6025,42 @@
           <t>ES2001-fixed-value_added</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5457,14 +6068,42 @@
           <t>ES2001-fixed-variable_capital</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SHAIKH_2020_SRAFFA_PRICES_T1T2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Shaikh (2020) An Empirically Sufficient Form for Sraffa Prices, Tables 1-2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Author working paper (festschrift for Pasinetti)</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>dimensionless ratios in [0.94, 1.08]</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>irregular (1947, 1958, 1963, 1967, 1972, 1998)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>academic-quotation / fair use of published table</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5647,11 +6286,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5674,54 +6313,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[5, 6, 7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{"dpr": "Technical/docs/series/ES2001_DPR.md", "epr": "Technical/docs/series/ES2001_EPR.md", "loader": "Technical/code/L01_loaders/L01_ES2001_load.py", "processor": "Technical/code/P02_processors/P02_ES2001_construct.py", "validator": "Technical/code/V03_validators/V03_ES2001_validate.py"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>last_updated</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>opus-fanout-ES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
